--- a/data/trans_camb/DCD-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/DCD-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 3,22</t>
+          <t>-3,13; 3,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,66; 17,58</t>
+          <t>9,66; 18,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 0,7</t>
+          <t>-6,23; 1,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,43; 23,15</t>
+          <t>15,8; 23,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 0,68</t>
+          <t>-4,37; 0,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,44; 19,88</t>
+          <t>14,29; 19,71</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-24,19; 29,77</t>
+          <t>-22,63; 28,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>71,29; 163,05</t>
+          <t>69,67; 162,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,39; 3,09</t>
+          <t>-24,31; 4,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59,32; 102,1</t>
+          <t>60,73; 104,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,68; 3,66</t>
+          <t>-21,5; 4,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,45; 110,27</t>
+          <t>69,93; 109,66</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 1,76</t>
+          <t>-1,02; 1,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 7,71</t>
+          <t>2,2; 7,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 0,64</t>
+          <t>-3,74; 0,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 10,77</t>
+          <t>2,27; 10,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,86</t>
+          <t>-1,69; 0,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,21; 8,77</t>
+          <t>3,52; 8,83</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-20,2; 42,71</t>
+          <t>-17,82; 42,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,47; 181,88</t>
+          <t>45,85; 178,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-29,06; 5,88</t>
+          <t>-28,11; 7,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,79; 95,73</t>
+          <t>18,24; 99,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,48; 12,07</t>
+          <t>-18,89; 11,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,13; 111,84</t>
+          <t>42,84; 114,64</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 4,91</t>
+          <t>0,12; 4,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,06; 8,17</t>
+          <t>3,12; 8,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 0,86</t>
+          <t>-6,26; 1,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,84; 13,54</t>
+          <t>5,83; 14,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 2,38</t>
+          <t>-2,25; 2,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,28; 10,3</t>
+          <t>5,35; 10,22</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 345,76</t>
+          <t>-7,5; 366,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>81,31; 588,82</t>
+          <t>71,39; 612,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-53,99; 13,64</t>
+          <t>-52,76; 17,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>45,11; 180,31</t>
+          <t>47,88; 195,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,74; 49,06</t>
+          <t>-31,79; 47,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>67,76; 214,87</t>
+          <t>68,84; 213,44</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,33</t>
+          <t>-1,17; 1,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,03; 7,31</t>
+          <t>3,13; 7,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,99; -1,57</t>
+          <t>-4,99; -1,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,3; 10,66</t>
+          <t>3,66; 10,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,8; -0,46</t>
+          <t>-2,6; -0,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,48; 8,6</t>
+          <t>4,45; 8,65</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 21,42</t>
+          <t>-16,06; 23,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>44,51; 119,02</t>
+          <t>45,75; 118,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-28,95; -9,75</t>
+          <t>-28,7; -10,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20,93; 67,11</t>
+          <t>22,86; 69,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,67; -4,03</t>
+          <t>-21,68; -4,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,21; 77,49</t>
+          <t>37,59; 77,62</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/DCD-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/DCD-Estudios-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13,66</t>
+          <t>12,46</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19,4</t>
+          <t>18,99</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,27</t>
+          <t>16,39</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 3,09</t>
+          <t>-3,49; 3,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,66; 18,07</t>
+          <t>8,61; 16,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 1,09</t>
+          <t>-7,06; 0,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,8; 23,53</t>
+          <t>15,38; 22,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 0,74</t>
+          <t>-4,27; 0,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,29; 19,71</t>
+          <t>13,76; 19,33</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>110,95%</t>
+          <t>101,16%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>85,33%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,63; 28,19</t>
+          <t>-25,2; 29,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>69,67; 162,83</t>
+          <t>61,53; 151,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-24,31; 4,63</t>
+          <t>-26,59; 2,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60,73; 104,67</t>
+          <t>56,89; 100,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,5; 4,03</t>
+          <t>-21,52; 4,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,93; 109,66</t>
+          <t>67,83; 107,12</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5,52</t>
+          <t>6,54</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,63</t>
+          <t>10,67</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,72</t>
+          <t>8,72</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,73</t>
+          <t>-1,26; 1,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 7,55</t>
+          <t>4,86; 8,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 0,79</t>
+          <t>-3,52; 0,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 10,91</t>
+          <t>8,44; 12,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,88</t>
+          <t>-1,86; 0,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,52; 8,83</t>
+          <t>7,35; 10,15</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>112,51%</t>
+          <t>133,11%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>105,45%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,82; 42,56</t>
+          <t>-21,16; 41,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>45,85; 178,21</t>
+          <t>80,42; 195,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,11; 7,35</t>
+          <t>-26,99; 4,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,24; 99,13</t>
+          <t>62,07; 118,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,89; 11,22</t>
+          <t>-20,02; 11,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,84; 114,64</t>
+          <t>81,71; 135,02</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5,63</t>
+          <t>5,61</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,84</t>
+          <t>10,47</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,88</t>
+          <t>8,23</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 4,91</t>
+          <t>0,04; 4,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,12; 8,07</t>
+          <t>3,11; 8,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 1,12</t>
+          <t>-6,38; 1,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,83; 14,01</t>
+          <t>6,36; 14,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 2,31</t>
+          <t>-2,09; 2,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,35; 10,22</t>
+          <t>5,78; 10,85</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>243,92%</t>
+          <t>243,0%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101,22%</t>
+          <t>107,77%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>133,06%</t>
+          <t>138,89%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 366,05</t>
+          <t>-3,23; 365,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>71,39; 612,22</t>
+          <t>72,04; 635,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-52,76; 17,49</t>
+          <t>-52,42; 14,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47,88; 195,17</t>
+          <t>50,9; 200,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-31,79; 47,82</t>
+          <t>-30,02; 47,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68,84; 213,44</t>
+          <t>75,75; 222,61</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5,63</t>
+          <t>6,27</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8,27</t>
+          <t>10,4</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,03</t>
+          <t>8,44</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,38</t>
+          <t>-1,15; 1,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,13; 7,2</t>
+          <t>4,78; 7,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,99; -1,6</t>
+          <t>-5,0; -1,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,66; 10,8</t>
+          <t>8,48; 12,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,6; -0,5</t>
+          <t>-2,77; -0,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,45; 8,65</t>
+          <t>7,35; 9,73</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>72,87%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 23,02</t>
+          <t>-15,67; 21,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>45,75; 118,2</t>
+          <t>65,67; 126,68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-28,7; -10,18</t>
+          <t>-28,8; -9,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22,86; 69,21</t>
+          <t>48,85; 79,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-21,68; -4,88</t>
+          <t>-22,61; -5,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,59; 77,62</t>
+          <t>60,18; 88,48</t>
         </is>
       </c>
     </row>
